--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-dr-person.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-dr-person.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2266" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="436">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:13:23+00:00</t>
+    <t>2026-06-19T14:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-person|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-person|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -388,7 +388,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>as-dr-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-person|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-person|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Person.meta.security</t>
@@ -655,7 +655,7 @@
     <t>as-ext-person-birth-place</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-birth-place|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-birth-place|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -675,7 +675,7 @@
     <t>as-ext-person-deceased-date-time</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Person.deceasedDateTime|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Person.deceasedDateTime|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -691,7 +691,7 @@
     <t>as-ext-person-statut-etat-civil</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-statut-etat-civil|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-statut-etat-civil|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -745,7 +745,7 @@
     <t>Person.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.1.0}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.2.0}
 </t>
   </si>
   <si>
@@ -779,7 +779,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order|5.3.0}
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
 </t>
   </si>
   <si>
@@ -805,6 +805,9 @@
   </si>
   <si>
     <t>required</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
@@ -908,10 +911,10 @@
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
   </si>
   <si>
-    <t>Civilités des personnes physiques du RASS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS|20221216120000</t>
+    <t>Civilités des personnes physiques</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS|20230331120000</t>
   </si>
   <si>
     <t>HumanName.prefix</t>
@@ -929,16 +932,10 @@
     <t>Person.name.suffix</t>
   </si>
   <si>
-    <t>jeu de valeurs pour spécifier le titre de la personne</t>
+    <t>Parts that come after the name</t>
   </si>
   <si>
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
-  </si>
-  <si>
-    <t>Civilités d'exercice d'un professionnel du RASS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS|20200424120000</t>
   </si>
   <si>
     <t>HumanName.suffix</t>
@@ -978,7 +975,7 @@
     <t>Person.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
@@ -1012,14 +1009,16 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
 </t>
   </si>
   <si>
     <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
-    <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>
+    <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
++ This extension allows to specify the type of mail used to contact the person.</t>
   </si>
   <si>
     <t>Person.telecom.system</t>
@@ -1370,7 +1369,7 @@
     <t>Person.link:as-practitioner-exercice-professionnel.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2)
 </t>
   </si>
   <si>
@@ -1719,7 +1718,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="87.8671875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="91.87890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="80.25390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4998,9 +4997,11 @@
       <c r="X29" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="Y29" s="2"/>
+      <c r="Y29" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5018,7 +5019,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5036,21 +5037,21 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5076,16 +5077,16 @@
         <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5134,7 +5135,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5152,25 +5153,25 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5192,13 +5193,13 @@
         <v>102</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5248,7 +5249,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5263,28 +5264,28 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5306,13 +5307,13 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5362,7 +5363,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5377,24 +5378,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5420,10 +5421,10 @@
         <v>102</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5453,10 +5454,10 @@
         <v>157</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5474,7 +5475,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5489,24 +5490,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5532,10 +5533,10 @@
         <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5562,31 +5563,31 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="Z34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5604,21 +5605,21 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>299</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5641,17 +5642,17 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5700,7 +5701,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5718,21 +5719,21 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5755,19 +5756,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5816,7 +5817,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5834,21 +5835,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>315</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5957,10 +5958,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6071,13 +6072,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>77</v>
@@ -6099,13 +6100,13 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6185,10 +6186,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6214,10 +6215,10 @@
         <v>175</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6247,28 +6248,28 @@
         <v>252</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Z40" t="s" s="2">
+      <c r="AA40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6277,7 +6278,7 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
@@ -6286,21 +6287,21 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6326,16 +6327,16 @@
         <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6384,7 +6385,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6402,21 +6403,21 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6442,16 +6443,16 @@
         <v>175</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6479,28 +6480,28 @@
         <v>252</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6518,21 +6519,21 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6555,16 +6556,16 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6614,7 +6615,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6643,10 +6644,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6669,13 +6670,13 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6726,7 +6727,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6744,7 +6745,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6755,10 +6756,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6784,16 +6785,16 @@
         <v>175</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6821,11 +6822,11 @@
         <v>252</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
       </c>
@@ -6842,7 +6843,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6857,24 +6858,24 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>368</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6897,19 +6898,19 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6958,7 +6959,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6973,24 +6974,24 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>377</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7013,19 +7014,19 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7074,7 +7075,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7092,21 +7093,21 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7129,13 +7130,13 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7186,7 +7187,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7204,21 +7205,21 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>391</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7241,17 +7242,17 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7300,7 +7301,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7318,7 +7319,7 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7329,10 +7330,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7355,17 +7356,17 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7414,7 +7415,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7432,10 +7433,10 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7443,10 +7444,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7469,13 +7470,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7514,7 +7515,7 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
@@ -7524,7 +7525,7 @@
         <v>115</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7542,7 +7543,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7553,10 +7554,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7665,10 +7666,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7779,14 +7780,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7808,10 +7809,10 @@
         <v>109</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>112</v>
@@ -7866,7 +7867,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7895,10 +7896,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7921,13 +7922,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7978,7 +7979,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>88</v>
@@ -7996,7 +7997,7 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8007,10 +8008,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8036,10 +8037,10 @@
         <v>175</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8069,11 +8070,11 @@
         <v>252</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>427</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8090,7 +8091,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8108,7 +8109,7 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8119,13 +8120,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C57" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
@@ -8147,13 +8148,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8204,7 +8205,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8222,7 +8223,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8233,10 +8234,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8345,10 +8346,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8459,14 +8460,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8488,10 +8489,10 @@
         <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>112</v>
@@ -8546,7 +8547,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8575,10 +8576,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8601,13 +8602,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8658,7 +8659,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>88</v>
@@ -8676,7 +8677,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8687,10 +8688,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8716,10 +8717,10 @@
         <v>175</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8749,11 +8750,11 @@
         <v>252</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>427</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
       </c>
@@ -8770,7 +8771,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8788,7 +8789,7 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>

--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-dr-person.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-dr-person.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2266" uniqueCount="437">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:20:56+00:00</t>
+    <t>2026-06-16T14:13:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-person|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-person|1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -388,7 +388,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>as-dr-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-person|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-person|1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Person.meta.security</t>
@@ -655,7 +655,7 @@
     <t>as-ext-person-birth-place</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-birth-place|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-birth-place|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -675,7 +675,7 @@
     <t>as-ext-person-deceased-date-time</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Person.deceasedDateTime|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Person.deceasedDateTime|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -691,7 +691,7 @@
     <t>as-ext-person-statut-etat-civil</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-statut-etat-civil|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-statut-etat-civil|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -745,7 +745,7 @@
     <t>Person.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.2.0}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.1.0}
 </t>
   </si>
   <si>
@@ -779,7 +779,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.3.0}
 </t>
   </si>
   <si>
@@ -805,9 +805,6 @@
   </si>
   <si>
     <t>required</t>
-  </si>
-  <si>
-    <t>The use of a human name.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
@@ -911,10 +908,10 @@
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
   </si>
   <si>
-    <t>Civilités des personnes physiques</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS|20230331120000</t>
+    <t>Civilités des personnes physiques du RASS</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS|20221216120000</t>
   </si>
   <si>
     <t>HumanName.prefix</t>
@@ -932,10 +929,16 @@
     <t>Person.name.suffix</t>
   </si>
   <si>
-    <t>Parts that come after the name</t>
+    <t>jeu de valeurs pour spécifier le titre de la personne</t>
   </si>
   <si>
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+  </si>
+  <si>
+    <t>Civilités d'exercice d'un professionnel du RASS</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS|20200424120000</t>
   </si>
   <si>
     <t>HumanName.suffix</t>
@@ -975,7 +978,7 @@
     <t>Person.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
 </t>
   </si>
   <si>
@@ -1009,16 +1012,14 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
 </t>
   </si>
   <si>
     <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
-    <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
-- This extension allows to specify the type of mail used to contact the person.</t>
+    <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>
   </si>
   <si>
     <t>Person.telecom.system</t>
@@ -1369,7 +1370,7 @@
     <t>Person.link:as-practitioner-exercice-professionnel.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-1)
 </t>
   </si>
   <si>
@@ -1718,7 +1719,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="87.8671875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="80.25390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="91.87890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4997,29 +4998,27 @@
       <c r="X29" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="Y29" t="s" s="2">
+      <c r="Y29" s="2"/>
+      <c r="Z29" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5037,21 +5036,21 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>257</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5077,16 +5076,16 @@
         <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5135,7 +5134,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5153,25 +5152,25 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>265</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5193,13 +5192,13 @@
         <v>102</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5249,7 +5248,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5264,28 +5263,28 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5307,13 +5306,13 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5363,7 +5362,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5378,24 +5377,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5421,10 +5420,10 @@
         <v>102</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5454,28 +5453,28 @@
         <v>157</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5490,24 +5489,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5533,10 +5532,10 @@
         <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5563,13 +5562,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>77</v>
+        <v>296</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5587,7 +5586,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5605,21 +5604,21 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5642,17 +5641,17 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5701,7 +5700,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5719,21 +5718,21 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5756,19 +5755,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5817,7 +5816,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5835,21 +5834,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5958,10 +5957,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6072,13 +6071,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="B39" t="s" s="2">
-        <v>316</v>
-      </c>
       <c r="C39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>77</v>
@@ -6100,13 +6099,13 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6186,10 +6185,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6215,10 +6214,10 @@
         <v>175</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6248,10 +6247,10 @@
         <v>252</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6269,7 +6268,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6278,7 +6277,7 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
@@ -6287,21 +6286,21 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6327,16 +6326,16 @@
         <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6385,7 +6384,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6403,21 +6402,21 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6443,16 +6442,16 @@
         <v>175</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6480,10 +6479,10 @@
         <v>252</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -6501,7 +6500,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6519,21 +6518,21 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6556,16 +6555,16 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6615,7 +6614,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6644,10 +6643,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6670,13 +6669,13 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6727,7 +6726,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6745,7 +6744,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6756,10 +6755,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6785,16 +6784,16 @@
         <v>175</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6822,10 +6821,10 @@
         <v>252</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -6843,7 +6842,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6858,24 +6857,24 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6898,19 +6897,19 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6959,7 +6958,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6974,24 +6973,24 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7014,19 +7013,19 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7075,7 +7074,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7093,21 +7092,21 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7130,13 +7129,13 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7187,7 +7186,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7205,21 +7204,21 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7242,17 +7241,17 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7301,7 +7300,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7319,7 +7318,7 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7330,10 +7329,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7356,17 +7355,17 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7415,7 +7414,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7433,10 +7432,10 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7444,10 +7443,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7470,13 +7469,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7515,7 +7514,7 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
@@ -7525,7 +7524,7 @@
         <v>115</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7543,7 +7542,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7554,10 +7553,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7666,10 +7665,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7780,14 +7779,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7809,10 +7808,10 @@
         <v>109</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>112</v>
@@ -7867,7 +7866,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7896,10 +7895,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7922,13 +7921,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7979,7 +7978,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>88</v>
@@ -7997,7 +7996,7 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8008,10 +8007,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8037,10 +8036,10 @@
         <v>175</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8070,10 +8069,10 @@
         <v>252</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8091,7 +8090,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8109,7 +8108,7 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8120,13 +8119,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
@@ -8148,13 +8147,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8205,7 +8204,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8223,7 +8222,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8234,10 +8233,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8346,10 +8345,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8460,14 +8459,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8489,10 +8488,10 @@
         <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>112</v>
@@ -8547,7 +8546,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8576,10 +8575,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8602,13 +8601,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8659,7 +8658,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>88</v>
@@ -8677,7 +8676,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8688,10 +8687,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8717,10 +8716,10 @@
         <v>175</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8750,10 +8749,10 @@
         <v>252</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -8771,7 +8770,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8789,7 +8788,7 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
